--- a/DATA/DISENO_EXPERIMENTAL/variables_predictoras.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/variables_predictoras.xlsx
@@ -425,108 +425,2461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Orden</t>
+          <t>Experimento</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Variable_Objetivo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Orden_Predictor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Variable_Predictora</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ranking_IPML</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IPML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Exp02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Exp03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Exp04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="E48" t="n">
+        <v>13</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>14</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="E59" t="n">
+        <v>14</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>12</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>14</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ONI</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Precipitacion_mm</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Radiacion_Solar</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="E74" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Humedad_Relativa</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Temp_Min_C</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VolumenUtilDiarioMasa</t>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>13</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>14</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Climática</t>
         </is>
       </c>
     </row>

--- a/DATA/DISENO_EXPERIMENTAL/variables_predictoras.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/variables_predictoras.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,25 +441,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Variable_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Orden_Predictor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Variable_Predictora</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ranking_IPML</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>IPML</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
@@ -476,21 +481,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -507,21 +517,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -538,21 +553,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -569,21 +589,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -600,21 +625,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -631,21 +661,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.95</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -662,21 +697,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.9</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -693,21 +733,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>13</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -724,21 +769,26 @@
           <t>irca</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>14</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -755,21 +805,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -786,21 +841,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -817,21 +877,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -848,21 +913,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -879,21 +949,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -910,21 +985,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -941,21 +1021,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>7</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>7</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.95</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -972,21 +1057,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>8</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>12</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.9</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1003,21 +1093,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>9</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>13</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -1034,21 +1129,26 @@
           <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>14</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1065,21 +1165,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -1096,21 +1201,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1127,21 +1237,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1158,21 +1273,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1189,21 +1309,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>5</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -1220,21 +1345,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>6</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>6</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -1251,21 +1381,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>7</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.95</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1282,21 +1417,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>8</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>12</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>0.9</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1313,21 +1453,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>13</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -1344,21 +1489,26 @@
           <t>Nivel_Minimo</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>14</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1375,21 +1525,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -1406,21 +1561,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1437,21 +1597,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1468,21 +1633,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>4</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1499,21 +1669,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>5</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -1530,21 +1705,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>6</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.95</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1561,21 +1741,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>7</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>12</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.9</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1592,21 +1777,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>8</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>13</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -1623,21 +1813,26 @@
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>9</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>14</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1654,21 +1849,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -1685,21 +1885,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>2</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -1716,21 +1921,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>3</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>3</v>
       </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1747,21 +1957,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>4</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1778,21 +1993,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>5</v>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -1809,21 +2029,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>6</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>6</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -1840,21 +2065,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>7</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>7</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.95</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1871,21 +2101,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>8</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>12</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.9</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1902,21 +2137,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>9</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>13</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -1933,21 +2173,26 @@
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>10</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>14</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -1964,21 +2209,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -1995,21 +2245,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>2</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>2</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2026,21 +2281,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>3</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>3</v>
       </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2057,21 +2317,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>4</v>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2088,21 +2353,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>5</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>5</v>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -2119,21 +2389,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>6</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>6</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -2150,21 +2425,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>7</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>7</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.95</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2181,21 +2461,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>8</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>12</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.9</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2212,21 +2497,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>9</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>13</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -2243,21 +2533,26 @@
           <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>10</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>14</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2274,21 +2569,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -2305,21 +2605,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>2</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>2</v>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2336,21 +2641,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>3</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2367,21 +2677,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>4</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>4</v>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2398,21 +2713,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>5</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>5</v>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -2429,21 +2749,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>6</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>6</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -2460,21 +2785,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>7</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>7</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>0.95</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2491,21 +2821,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>8</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>12</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>0.9</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2522,21 +2857,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>9</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>13</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -2553,21 +2893,26 @@
           <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>10</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>14</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2584,21 +2929,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>ONI</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>Variabilidad Climática</t>
         </is>
@@ -2615,21 +2965,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>2</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>2</v>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
@@ -2646,21 +3001,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>3</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Precipitacion_mm</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2677,21 +3037,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>4</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Radiacion_Solar</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>4</v>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2708,21 +3073,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>5</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>5</v>
       </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
@@ -2739,21 +3109,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>6</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>6</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>0.9636</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
@@ -2770,21 +3145,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>7</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Humedad_Relativa</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>7</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>0.95</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2801,21 +3181,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>8</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Temp_Min_C</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>12</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>0.9</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
@@ -2832,21 +3217,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
         <v>9</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>13</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
@@ -2863,21 +3253,26 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
         <v>10</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Velocidad_Viento</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>14</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>0.8668</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
